--- a/Labs/Lab9/Assignment9Rubric-DomainModel-UML-Scaffolding.xlsx
+++ b/Labs/Lab9/Assignment9Rubric-DomainModel-UML-Scaffolding.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repos\CS246-Repos\CS246-CourseMaterials\Labs\Lab9\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9726B446-DCE4-4013-950C-791985BA7486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D66359E2-A102-4AC1-88A9-E8066D4B4CC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13272" yWindow="2484" windowWidth="17028" windowHeight="14244" activeTab="1" xr2:uid="{2ED55EEA-81A7-FF44-BCE3-68AB9ADB8259}"/>
+    <workbookView xWindow="31896" yWindow="4824" windowWidth="18096" windowHeight="12336" activeTab="1" xr2:uid="{2ED55EEA-81A7-FF44-BCE3-68AB9ADB8259}"/>
   </bookViews>
   <sheets>
     <sheet name="Rubric" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="27">
   <si>
     <t>Requirements</t>
   </si>
@@ -94,13 +94,37 @@
   </si>
   <si>
     <t>Relationship lines</t>
+  </si>
+  <si>
+    <t>Database</t>
+  </si>
+  <si>
+    <t>Correct</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>Yes, in-memory</t>
+  </si>
+  <si>
+    <t>Exellent work designing a domain model and building a prototype to test it.</t>
+  </si>
+  <si>
+    <t>Complete</t>
+  </si>
+  <si>
+    <t>Here's the grade breakdown:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -164,6 +188,11 @@
       <name val="Helvetica"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Helvetica"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -185,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -199,14 +228,23 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -522,7 +560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFCD13E5-EC24-C14D-9BEE-EA2BBE4DEF6B}">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.69921875" customWidth="1"/>
@@ -564,7 +602,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -580,7 +618,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -589,7 +627,7 @@
       </c>
       <c r="B9" s="1">
         <f>SUM(B6:B8)</f>
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -639,7 +677,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B17" s="2">
         <v>10</v>
@@ -647,45 +685,49 @@
     </row>
     <row r="18" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
+      <c r="B19" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B19" s="1">
-        <f>SUM(B17:B18)</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="4"/>
-      <c r="B20" s="2"/>
+      <c r="B20" s="1">
+        <f>SUM(B17:B19)</f>
+        <v>40</v>
+      </c>
     </row>
     <row r="21" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7"/>
+      <c r="B21" s="1"/>
+    </row>
+    <row r="22" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B21" s="1">
-        <f>SUM(B9,B14,B19)</f>
+      <c r="B22" s="1">
+        <f>SUM(B9,B14,B20)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="4"/>
-      <c r="B22" s="2"/>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
+    <row r="23" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="4"/>
+      <c r="B23" s="2"/>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="4"/>
-      <c r="B24" s="2"/>
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="4"/>
@@ -699,9 +741,13 @@
       <c r="A27" s="4"/>
       <c r="B27" s="2"/>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="4"/>
+      <c r="B28" s="2"/>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -711,7 +757,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8EF6DB9-5046-F545-B378-AB8AF91CAAF1}">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.296875" customWidth="1"/>
@@ -733,260 +779,314 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="13" customFormat="1" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="11"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="15"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+    </row>
+    <row r="5" spans="1:6" s="11" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="6" t="s">
+      <c r="B6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="E5" s="9"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="E7" s="9"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B8" s="2">
+        <v>15</v>
+      </c>
+      <c r="C8" s="2">
+        <v>15</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="2">
-        <v>20</v>
-      </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="10">
-        <f>C6/B6</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="2">
-        <v>10</v>
-      </c>
-      <c r="C7" s="2">
-        <v>10</v>
-      </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="10">
-        <f>C7/B7</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2">
-        <v>10</v>
-      </c>
-      <c r="C8" s="2">
-        <v>10</v>
-      </c>
-      <c r="E8" s="9"/>
       <c r="F8" s="10">
         <f>C8/B8</f>
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="1">
-        <f>SUM(B6:B8)</f>
-        <v>40</v>
-      </c>
-      <c r="C9" s="1">
-        <f>SUM(C6:C8)</f>
-        <v>40</v>
-      </c>
-      <c r="E9" s="9"/>
+      <c r="A9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="2">
+        <v>10</v>
+      </c>
+      <c r="C9" s="2">
+        <v>10</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>20</v>
+      </c>
       <c r="F9" s="10">
         <f>C9/B9</f>
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="4"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="10"/>
+      <c r="A10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="2">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2">
+        <v>5</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="10">
+        <f>C10/B10</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="1">
+        <f>SUM(B8:B10)</f>
+        <v>30</v>
+      </c>
+      <c r="C11" s="1">
+        <f>SUM(C8:C10)</f>
+        <v>30</v>
+      </c>
+      <c r="E11" s="9"/>
+      <c r="F11" s="10">
+        <f>C11/B11</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="4"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="10"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="10"/>
-    </row>
-    <row r="12" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2">
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="10"/>
+    </row>
+    <row r="14" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="2">
         <v>20</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C14" s="2">
         <v>20</v>
       </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="10">
-        <f>C12/B12</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2">
-        <v>10</v>
-      </c>
-      <c r="C13" s="2">
-        <v>10</v>
-      </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="10">
-        <f>C13/B13</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="1">
-        <f>SUM(B12:B13)</f>
-        <v>30</v>
-      </c>
-      <c r="C14" s="1">
-        <f>SUM(C12:C13)</f>
-        <v>30</v>
-      </c>
-      <c r="E14" s="9"/>
+      <c r="E14" s="9" t="s">
+        <v>21</v>
+      </c>
       <c r="F14" s="10">
         <f>C14/B14</f>
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="4"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="10"/>
+      <c r="A15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="2">
+        <v>10</v>
+      </c>
+      <c r="C15" s="2">
+        <v>10</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="10">
+        <f>C15/B15</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="1">
+        <f>SUM(B14:B15)</f>
+        <v>30</v>
+      </c>
+      <c r="C16" s="1">
+        <f>SUM(C14:C15)</f>
+        <v>30</v>
+      </c>
+      <c r="E16" s="9"/>
+      <c r="F16" s="10">
+        <f>C16/B16</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="4"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="10"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="10"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="2">
-        <v>15</v>
-      </c>
-      <c r="C17" s="2">
-        <v>15</v>
-      </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="10">
-        <f>C17/B17</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="2">
-        <v>15</v>
-      </c>
-      <c r="C18" s="2">
-        <v>15</v>
-      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
       <c r="E18" s="9"/>
-      <c r="F18" s="10">
-        <f>C18/B18</f>
-        <v>1</v>
-      </c>
+      <c r="F18" s="10"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" s="1">
-        <f>SUM(B17:B18)</f>
-        <v>30</v>
-      </c>
-      <c r="C19" s="1">
-        <f>SUM(C17:C18)</f>
-        <v>30</v>
-      </c>
-      <c r="E19" s="9"/>
+      <c r="A19" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="2">
+        <v>10</v>
+      </c>
+      <c r="C19" s="2">
+        <v>10</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>23</v>
+      </c>
       <c r="F19" s="10">
         <f>C19/B19</f>
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="4"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="E20" s="9"/>
+      <c r="A20" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="2">
+        <v>10</v>
+      </c>
+      <c r="C20" s="2">
+        <v>10</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="10">
+        <f>C20/B20</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="2">
+        <v>20</v>
+      </c>
+      <c r="C21" s="2">
+        <v>20</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="10">
+        <f>C21/B21</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="1">
+        <f>SUM(B19:B21)</f>
+        <v>40</v>
+      </c>
+      <c r="C22" s="1">
+        <f>SUM(C19:C21)</f>
+        <v>40</v>
+      </c>
+      <c r="E22" s="9"/>
+      <c r="F22" s="10">
+        <f>C22/B22</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="4"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="E23" s="9"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B21" s="1">
-        <f>SUM(B9,B14,B19)</f>
+      <c r="B24" s="1">
+        <f>SUM(B11,B16,B22)</f>
         <v>100</v>
       </c>
-      <c r="C21" s="1">
-        <f>SUM(C9,C14,C19)</f>
+      <c r="C24" s="1">
+        <f>SUM(C11,C16,C22)</f>
         <v>100</v>
       </c>
-      <c r="E21" s="9"/>
+      <c r="E24" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
+    <mergeCell ref="A5:F5"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A4:F4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
